--- a/data/raw/conversations_source_02.xlsx
+++ b/data/raw/conversations_source_02.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tickets" sheetId="1" r:id="Rd1bbb138ae284b6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="2" r:id="R95596506ff5a4084"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="3" r:id="R66d66cd26b2947c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Counts" sheetId="4" r:id="Ra909f58ad8b64943"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tickets" sheetId="1" r:id="Raa0f2f155a344c3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="2" r:id="Rf84b0767d1844283"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="3" r:id="Rb3db34a56db84d79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Counts" sheetId="4" r:id="Re773aa10a13b498c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -46,13 +46,7 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -402,25 +396,31 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>Frustrated</x:v>
+        <x:v>Angry</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Opening a large photo-upload session kills browsing for a minute, then it comes back. The path test flags MTU trouble on the fiber connection.</x:v>
+        <x:v>Our broadband session disconnects after a long period without traffic, then reconnects when we use it. The session settings show an idle timeout. I am angry about this situation and want it addressed.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Customer: Opening a large photo-upload session kills browsing for a minute, then it comes back. The path test flags MTU trouble on the fiber connection.
-Agent: Do approved path-MTU diagnostics identify a verified encapsulation mismatch?
-Customer: They confirm the mismatch; the supported MTU correction removed the upload-triggered stalls.
-Agent: Correcting the verified access MTU mismatch stopped large-transfer connection stalls.</x:v>
+        <x:v>Customer: Our broadband session disconnects after a long period without traffic, then reconnects when we use it. The session settings show an idle timeout. I am angry about this situation and want it addressed.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Inspect broadband session policy and idle-timeout logs.
+2. Distinguish deliberate session shutdown from a line fault.
+3. Enable the supported always-on session policy with authorisation.
+4. Test access after an extended idle period.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>1. Compare normal browsing and large-transfer failures.
-2. Run approved path-MTU diagnostics for the provisioned access architecture.
-3. Correct the verified MTU configuration through authorised support.
-4. Verify uploads and other internet sessions together.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Inspect broadband session policy and idle-timeout logs.
+2. Distinguish deliberate session shutdown from a line fault.
+3. Enable the supported always-on session policy with authorisation.
+4. Test access after an extended idle period.</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
-        <x:v>Correcting the verified access MTU mismatch stopped large-transfer connection stalls.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L2" s="3" t="str">
         <x:v>approved for historical</x:v>
@@ -447,7 +447,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G3" s="3" t="str">
-        <x:v>Urgent</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H3" s="3" t="str">
         <x:v>We put in a cupboard and squeezed the thin cable behind it. Now the little optical light complains whenever the cupboard moves and the internet flickers. Leaving it alone for now.</x:v>
@@ -537,7 +537,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G5" s="3" t="str">
-        <x:v>Annoyed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H5" s="3" t="str">
         <x:v>TV box on, internet gone. TV box off, internet back. Every phone does it. Can someone work out what the television is doing to the network?</x:v>
@@ -672,7 +672,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G8" s="3" t="str">
-        <x:v>Disappointed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
         <x:v>Several apartments lose fiber at the same instant because the access platform repeatedly restarts. Our ONTs aren't rebooting; support has the matching equipment alarm.</x:v>
@@ -762,7 +762,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G10" s="3" t="str">
-        <x:v>Annoyed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H10" s="3" t="str">
         <x:v>Still using the connection, still getting booted off at the exact session-lifetime limit. There is a failed renewal message in the support logs. This cannot be the intended behaviour.</x:v>
@@ -804,28 +804,34 @@
         <x:v>Fiber Broadband &amp; Gateway</x:v>
       </x:c>
       <x:c r="F11" s="3" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="G11" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Angry</x:v>
       </x:c>
       <x:c r="H11" s="3" t="str">
-        <x:v>One ancient work PC downloads like a snail. Same cable setup, newer laptop flies. Its administrator found a restrictive receive setting; could you help confirm the supported fix?</x:v>
+        <x:v>Our router still has a 50 Mbps traffic-shaping limit although the fibre service has been upgraded. Both uploads and downloads stop near that value. I am angry about this situation and want it addressed.</x:v>
       </x:c>
       <x:c r="I11" s="3" t="str">
-        <x:v>Customer: One ancient work PC downloads like a snail. Same cable setup, newer laptop flies. Its administrator found a restrictive receive setting; could you help confirm the supported fix?
-Agent: Does approved endpoint testing isolate the throughput restriction to that workstation setting?
-Customer: Yes; the administrator restored supported defaults and its transfer speed recovered.
-Agent: Restoring supported endpoint transport defaults removed the workstation-specific throughput limit.</x:v>
+        <x:v>Customer: Our router still has a 50 Mbps traffic-shaping limit although the fibre service has been upgraded. Both uploads and downloads stop near that value. I am angry about this situation and want it addressed.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Compare subscribed bandwidth with configured traffic-shaping rates.
+2. Check for other load or line limitations.
+3. Update shaping to approved values appropriate to the service.
+4. Verify throughput and prioritisation after the change.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>1. Compare controlled wired throughput across devices.
-2. Inspect endpoint transport settings through the authorised administrator.
-3. Restore vendor-supported transport defaults where the restriction is confirmed.
-4. Retest without altering required security controls.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Compare subscribed bandwidth with configured traffic-shaping rates.
+2. Check for other load or line limitations.
+3. Update shaping to approved values appropriate to the service.
+4. Verify throughput and prioritisation after the change.</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
-        <x:v>Restoring supported endpoint transport defaults removed the workstation-specific throughput limit.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L11" s="3" t="str">
         <x:v>approved for historical</x:v>
@@ -942,7 +948,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G14" s="3" t="str">
-        <x:v>Urgent</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H14" s="3" t="str">
         <x:v>Uploads slow dramatically when one damaged client floods the network with broadcast traffic. It has been isolated by our administrator for testing.</x:v>
@@ -1032,7 +1038,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G16" s="3" t="str">
-        <x:v>Disappointed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H16" s="3" t="str">
         <x:v>File sync crawls through our customer-managed tunnel because packets are being fragmented repeatedly. Plain approved measurements of the fiber circuit are normal.</x:v>
@@ -1077,7 +1083,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G17" s="3" t="str">
-        <x:v>Annoyed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H17" s="3" t="str">
         <x:v>Traffic takes an unnecessarily long route after a backup transit path remained selected. There isn't a local Wi-Fi or cable problem.</x:v>
@@ -1122,7 +1128,7 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="G18" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H18" s="3" t="str">
         <x:v>Oops, the file-download tool has its own tiny speed limit. Another tool is fast on this connection. Please help me change that setting without altering the package.</x:v>
@@ -1209,10 +1215,10 @@
         <x:v>Fiber Broadband &amp; Gateway</x:v>
       </x:c>
       <x:c r="F20" s="3" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="G20" s="3" t="str">
-        <x:v>Panicked</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H20" s="3" t="str">
         <x:v>Upstream firewall policy accidentally denies all subscriber traffic on our business circuit. A reviewed change record matches the start of this total outage.</x:v>
@@ -1302,7 +1308,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G22" s="3" t="str">
-        <x:v>Urgent</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H22" s="3" t="str">
         <x:v>The ONT was registered under the wrong access-port identifier after a planned move. Nothing works; we have the authorised move reference.</x:v>
@@ -1392,7 +1398,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G24" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H24" s="3" t="str">
         <x:v>Only IPv6 access is provisioned correctly; IPv4 session translation is unavailable because the provider translation pool failed. Ordinary required services won't open.</x:v>
@@ -1482,25 +1488,31 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G26" s="3" t="str">
-        <x:v>Urgent</x:v>
+        <x:v>Angry</x:v>
       </x:c>
       <x:c r="H26" s="3" t="str">
-        <x:v>Backup protection didn't transfer the access uplink after its primary optical module failed. Our office is entirely offline despite the planned protected service.</x:v>
+        <x:v>Our internet stopped completely after IPv6 was disabled. This fibre service uses DS-Lite for IPv4, so its required IPv6 transport is now unavailable. I am angry about this situation and want it addressed.</x:v>
       </x:c>
       <x:c r="I26" s="3" t="str">
-        <x:v>Customer: Backup protection didn't transfer the access uplink after its primary optical module failed. Our office is entirely offline despite the planned protected service.
-Agent: Do authorised alarms confirm primary failure and a protection-switching fault?
-Customer: Operations confirmed both and restored the eligible protected path.
-Agent: Restoring the approved protected uplink recovered the office's failed access service.</x:v>
+        <x:v>Customer: Our internet stopped completely after IPv6 was disabled. This fibre service uses DS-Lite for IPv4, so its required IPv6 transport is now unavailable. I am angry about this situation and want it addressed.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Confirm the provisioned access architecture and supported settings.
+2. Inspect DS-Lite tunnel and IPv6 transport status.
+3. Restore the approved required configuration with consent.
+4. Verify IPv4 and IPv6 service access.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J26" s="3" t="str">
-        <x:v>1. Inspect access-uplink alarms and the contracted protection arrangement.
-2. Verify failure of the primary module and supported protection state.
-3. Repair or restore the protected path through authorised operations.
-4. Test access recovery and an approved protection check.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Confirm the provisioned access architecture and supported settings.
+2. Inspect DS-Lite tunnel and IPv6 transport status.
+3. Restore the approved required configuration with consent.
+4. Verify IPv4 and IPv6 service access.</x:v>
       </x:c>
       <x:c r="K26" s="3" t="str">
-        <x:v>Restoring the approved protected uplink recovered the office's failed access service.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L26" s="3" t="str">
         <x:v>approved for historical</x:v>
@@ -1527,7 +1539,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G27" s="3" t="str">
-        <x:v>Disappointed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H27" s="3" t="str">
         <x:v>Activation looks complete but the service is tied to a retired broadband identifier after an account migration. The new identifier never received the access entitlement.</x:v>
@@ -1572,7 +1584,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G28" s="3" t="str">
-        <x:v>Annoyed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H28" s="3" t="str">
         <x:v>Someone disabled the managed firewall internet interface during a change. LAN is fine, outside access is completely dead. We have the authorised admin ready to check it.</x:v>
@@ -1617,7 +1629,7 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="G29" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H29" s="3" t="str">
         <x:v>Everything connects but the screen on the box is blank. Our caretaker relies on that display and thinks the entire service has failed. Can you check the screen separately?</x:v>
@@ -1662,7 +1674,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G30" s="3" t="str">
-        <x:v>Panicked</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H30" s="3" t="str">
         <x:v>A safety inspection found electrical leakage at the gateway enclosure. We stopped using it and need qualified handling, not more reboot instructions.</x:v>
@@ -1707,7 +1719,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G31" s="3" t="str">
-        <x:v>Annoyed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H31" s="3" t="str">
         <x:v>Power button broke clean off the gateway. No, we have not opened it or poked anything into the hole. Need the proper replacement route.</x:v>
@@ -1842,7 +1854,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G34" s="3" t="str">
-        <x:v>Urgent</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H34" s="3" t="str">
         <x:v>Gateway missing from the property, ONT still on the wall. We cannot get online without the rented box. What is the official verified replacement process?</x:v>
@@ -1887,7 +1899,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G35" s="3" t="str">
-        <x:v>Disappointed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H35" s="3" t="str">
         <x:v>The vendor power connector on this newly delivered gateway is the wrong compatible type for the supplied unit. We have not forced it or tried substitute adapters.</x:v>
@@ -1932,7 +1944,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G36" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H36" s="3" t="str">
         <x:v>Gateway refuses to boot and hardware support identifies a failed internal clock component. The supported recovery test didn't recover it.</x:v>
@@ -1977,25 +1989,31 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G37" s="3" t="str">
-        <x:v>Urgent</x:v>
+        <x:v>Angry</x:v>
       </x:c>
       <x:c r="H37" s="3" t="str">
-        <x:v>Our rack router has failed its redundant power-module self-test. It's still on one module, but that leaves no planned power resilience.</x:v>
+        <x:v>The gateway external antenna broke when a shelf fell. Wired internet still works, but Wi-Fi reception became poor immediately afterwards. I am angry about this situation and want it addressed.</x:v>
       </x:c>
       <x:c r="I37" s="3" t="str">
-        <x:v>Customer: Our rack router has failed its redundant power-module self-test. It's still on one module, but that leaves no planned power resilience.
-Agent: Does authorised monitoring identify the failed redundant module and a supported replacement?
-Customer: It does; qualified maintenance replaced the failed module using the approved process.
-Agent: Qualified replacement restored the managed router's planned power redundancy.</x:v>
+        <x:v>Customer: The gateway external antenna broke when a shelf fell. Wired internet still works, but Wi-Fi reception became poor immediately afterwards. I am angry about this situation and want it addressed.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Compare wired service with wireless behaviour.
+2. Document visible antenna damage without dismantling equipment.
+3. Arrange approved antenna or router replacement according to the model.
+4. Verify wireless coverage on the replacement hardware.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J37" s="3" t="str">
-        <x:v>1. Review model-specific redundancy alarms.
-2. Validate the failed module through authorised equipment diagnostics.
-3. Have qualified maintenance replace it using supported continuity procedures.
-4. Verify both power sources and service operation.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Compare wired service with wireless behaviour.
+2. Document visible antenna damage without dismantling equipment.
+3. Arrange approved antenna or router replacement according to the model.
+4. Verify wireless coverage on the replacement hardware.</x:v>
       </x:c>
       <x:c r="K37" s="3" t="str">
-        <x:v>Qualified replacement restored the managed router's planned power redundancy.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L37" s="3" t="str">
         <x:v>approved for historical</x:v>
@@ -2112,7 +2130,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G40" s="3" t="str">
-        <x:v>Annoyed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H40" s="3" t="str">
         <x:v>Our signed bundle includes one recurring line rental, but the combined bill adds a second component that the accepted terms don't support.</x:v>
@@ -2157,25 +2175,31 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G41" s="3" t="str">
-        <x:v>Disappointed</x:v>
+        <x:v>Angry</x:v>
       </x:c>
       <x:c r="H41" s="3" t="str">
-        <x:v>Credit from the previous bill was meant to carry forward; the new statement starts at zero and ignores it. Please trace the actual balance transfer.</x:v>
+        <x:v>My final telecom bill contains a gateway non-return fee, but the depot receipt records the returned router with the matching serial number. I am angry about this situation and want it addressed.</x:v>
       </x:c>
       <x:c r="I41" s="3" t="str">
-        <x:v>Customer: Credit from the previous bill was meant to carry forward; the new statement starts at zero and ignores it. Please trace the actual balance transfer.
-Agent: Do ledger records confirm a valid credit that failed to carry forward?
-Customer: They do; the authorised transfer reconciliation restored it.
-Agent: Restoring a verified carried-forward credit corrected the opening invoice balance.</x:v>
+        <x:v>Customer: My final telecom bill contains a gateway non-return fee, but the depot receipt records the returned router with the matching serial number. I am angry about this situation and want it addressed.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Verify the equipment serial and authorised return reference.
+2. Reconcile courier and depot receipt records.
+3. Correct the validated return status and remove the ineligible fee through billing.
+4. Issue the revised final balance.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J41" s="3" t="str">
-        <x:v>1. Review the prior closing credit and new opening balance.
-2. Inspect the balance-transfer records.
-3. Reconcile the verified missing credit through authorised accounting controls.
-4. Confirm the new statement reflects the correct balance.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Verify the equipment serial and authorised return reference.
+2. Reconcile courier and depot receipt records.
+3. Correct the validated return status and remove the ineligible fee through billing.
+4. Issue the revised final balance.</x:v>
       </x:c>
       <x:c r="K41" s="3" t="str">
-        <x:v>Restoring a verified carried-forward credit corrected the opening invoice balance.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L41" s="3" t="str">
         <x:v>approved for historical</x:v>
@@ -2247,7 +2271,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G43" s="3" t="str">
-        <x:v>Panicked</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H43" s="3" t="str">
         <x:v>One account's credit was applied to another customer's balance during consolidation. This needs a controlled financial and privacy review.</x:v>
@@ -2517,25 +2541,31 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="G49" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Angry</x:v>
       </x:c>
       <x:c r="H49" s="3" t="str">
-        <x:v>Can we lower the permitted out-of-bundle spend cap without changing the base tariff? I'd like to know which charges the cap actually covers.</x:v>
+        <x:v>I would like an eligible mobile roaming option for my planned destinations. Please explain its documented price, validity and limits before I decide. I am angry about this situation and want it addressed.</x:v>
       </x:c>
       <x:c r="I49" s="3" t="str">
-        <x:v>Customer: Can we lower the permitted out-of-bundle spend cap without changing the base tariff? I'd like to know which charges the cap actually covers.
-Agent: Do the documented plan controls allow the requested eligible cap change?
-Customer: Yes; its scope was explained and I approved the supported new cap.
-Agent: An authorised spending-control update applied the accepted eligible cap.</x:v>
+        <x:v>Customer: I would like an eligible mobile roaming option for my planned destinations. Please explain its documented price, validity and limits before I decide. I am angry about this situation and want it addressed.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Review destination eligibility and current roaming entitlement.
+2. Explain documented option price validity and limits.
+3. Activate the customer-approved eligible roaming option.
+4. Verify entitlement before travel.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J49" s="3" t="str">
-        <x:v>1. Verify account authority and available spending controls.
-2. Explain documented covered charges and exclusions.
-3. Apply the eligible customer-approved cap.
-4. Confirm the setting without promising it blocks every possible charge.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Review destination eligibility and current roaming entitlement.
+2. Explain documented option price validity and limits.
+3. Activate the customer-approved eligible roaming option.
+4. Verify entitlement before travel.</x:v>
       </x:c>
       <x:c r="K49" s="3" t="str">
-        <x:v>An authorised spending-control update applied the accepted eligible cap.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L49" s="3" t="str">
         <x:v>approved for historical</x:v>
@@ -2607,7 +2637,7 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="G51" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H51" s="3" t="str">
         <x:v>Our team needs a supported mobile tethering allowance. Please explain eligibility and limits before anyone uses the SIM as a work hotspot.</x:v>
@@ -2787,7 +2817,7 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="G55" s="3" t="str">
-        <x:v>Annoyed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H55" s="3" t="str">
         <x:v>Remove an optional voicemail transcription feature but keep ordinary voicemail active. Last time a general removal request caused confusion, so I'm being specific.</x:v>
@@ -2922,7 +2952,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G58" s="3" t="str">
-        <x:v>Disappointed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H58" s="3" t="str">
         <x:v>Signal has been fading across several households, not just on my phone. Site maintenance says a damaged antenna feeder is confirmed. Can we track the qualified repair?</x:v>
@@ -2964,28 +2994,34 @@
         <x:v>Mobile Postpaid / SIM</x:v>
       </x:c>
       <x:c r="F59" s="3" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="G59" s="3" t="str">
-        <x:v>Urgent</x:v>
+        <x:v>Angry</x:v>
       </x:c>
       <x:c r="H59" s="3" t="str">
-        <x:v>Data continues working, but voice loses registration because the network's supported voice-registration refresh is failing. Device and entitlement checks pass.</x:v>
+        <x:v>My mobile reception becomes poor with a decorative metal phone cover fitted. Removing that accessory restores normal reception at the same location. I am angry about this situation and want it addressed.</x:v>
       </x:c>
       <x:c r="I59" s="3" t="str">
-        <x:v>Customer: Data continues working, but voice loses registration because the network's supported voice-registration refresh is failing. Device and entitlement checks pass.
-Agent: Have voice-service logs identified the registration refresh failure?
-Customer: Yes; the authorised voice-platform correction restored stable registration.
-Agent: A voice-platform refresh correction restored stable supported calling registration.</x:v>
+        <x:v>Customer: My mobile reception becomes poor with a decorative metal phone cover fitted. Removing that accessory restores normal reception at the same location. I am angry about this situation and want it addressed.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Compare reception with and without the removable accessory.
+2. Verify no concurrent network incident.
+3. Recommend a compatible accessory according to manufacturer guidance.
+4. Confirm normal registration without the obstructing case.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J59" s="3" t="str">
-        <x:v>1. Verify supported handset and voice entitlement.
-2. Inspect authorised voice-registration refresh traces.
-3. Correct the confirmed platform handling fault.
-4. Test registration stability and incoming and outgoing calls.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Compare reception with and without the removable accessory.
+2. Verify no concurrent network incident.
+3. Recommend a compatible accessory according to manufacturer guidance.
+4. Confirm normal registration without the obstructing case.</x:v>
       </x:c>
       <x:c r="K59" s="3" t="str">
-        <x:v>A voice-platform refresh correction restored stable supported calling registration.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L59" s="3" t="str">
         <x:v>approved for historical</x:v>
@@ -3057,7 +3093,7 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="G61" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H61" s="3" t="str">
         <x:v>Two SIMs, one phone: start a call on one and the other goes unavailable. Is this what dual standby actually means? Please explain before calling it a tower fault.</x:v>
@@ -3102,7 +3138,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G62" s="3" t="str">
-        <x:v>Annoyed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H62" s="3" t="str">
         <x:v>Our test devices fail on an enabled radio combination that the handset firmware doesn't support correctly. Single supported bands work normally.</x:v>
@@ -3147,7 +3183,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G63" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H63" s="3" t="str">
         <x:v>The handset tries to stay on our home network where only an eligible domestic roaming partner is available. Automatic permitted partner selection is misconfigured.</x:v>
@@ -3237,7 +3273,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G65" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H65" s="3" t="str">
         <x:v>Activation screen lists the OLD phone identifier. This eSIM is meant for the replacement handset. We stopped rather than download a profile to the wrong device.</x:v>
@@ -3327,7 +3363,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G67" s="3" t="str">
-        <x:v>Urgent</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H67" s="3" t="str">
         <x:v>Porting order stayed locked to a cancelled transfer request. The new accepted request cannot progress until that obsolete order lock is cleared.</x:v>
@@ -3372,7 +3408,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G68" s="3" t="str">
-        <x:v>Annoyed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H68" s="3" t="str">
         <x:v>Apparently this is a duplicate subscription, except the secure review team says it is not. That false-match hold is still blocking the new line. Please finish the approved release.</x:v>
@@ -3507,7 +3543,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G71" s="3" t="str">
-        <x:v>Disappointed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H71" s="3" t="str">
         <x:v>Temporary mobile number should have been replaced by the confirmed ported number, but the device still presents the temporary one to callers.</x:v>
@@ -3552,7 +3588,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G72" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H72" s="3" t="str">
         <x:v>Two accepted SIM replacements were submitted accidentally, and the account is waiting on the superseded order instead of the approved latest one.</x:v>
@@ -3594,28 +3630,34 @@
         <x:v>Mobile Postpaid / SIM</x:v>
       </x:c>
       <x:c r="F73" s="3" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="G73" s="3" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Angry</x:v>
       </x:c>
       <x:c r="H73" s="3" t="str">
-        <x:v>The business eSIM fleet installation failed because our management tool assigned the wrong device inventory entry. The carrier profile itself is valid.</x:v>
+        <x:v>My mobile calling service is unavailable on the new eSIM. The profile is valid, but the handset remains locked to its original carrier. I am angry about this situation and want it addressed.</x:v>
       </x:c>
       <x:c r="I73" s="3" t="str">
-        <x:v>Customer: The business eSIM fleet installation failed because our management tool assigned the wrong device inventory entry. The carrier profile itself is valid.
-Agent: Does the authorised device-management review confirm the local inventory mismatch?
-Customer: Yes; the enterprise administrator corrected it and installed the eligible profile.
-Agent: Correcting the enterprise device inventory assignment enabled eligible eSIM deployment.</x:v>
+        <x:v>Customer: My mobile calling service is unavailable on the new eSIM. The profile is valid, but the handset remains locked to its original carrier. I am angry about this situation and want it addressed.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Verify device compatibility and documented lock state without requesting secret codes.
+2. Explain the original carrier's authorised unlock requirement.
+3. Proceed only after confirmed eligible unlock or supported replacement device.
+4. Verify registration of the authorised eSIM.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J73" s="3" t="str">
-        <x:v>1. Verify authorised administrator and intended eligible device.
-2. Compare fleet inventory assignment with the approved profile order.
-3. Correct the local inventory association through controlled administration.
-4. Verify authorised installation and registration.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Verify device compatibility and documented lock state without requesting secret codes.
+2. Explain the original carrier's authorised unlock requirement.
+3. Proceed only after confirmed eligible unlock or supported replacement device.
+4. Verify registration of the authorised eSIM.</x:v>
       </x:c>
       <x:c r="K73" s="3" t="str">
-        <x:v>Correcting the enterprise device inventory assignment enabled eligible eSIM deployment.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L73" s="3" t="str">
         <x:v>approved for historical</x:v>
@@ -3642,7 +3684,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G74" s="3" t="str">
-        <x:v>Disappointed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H74" s="3" t="str">
         <x:v>New home fiber order was surveyed as aerial when the approved route is underground. The work pack needs correction before the appropriate crew arrives.</x:v>
@@ -3732,7 +3774,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G76" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H76" s="3" t="str">
         <x:v>The new cable was installed but its labeling points to the wrong premises record at the distribution point. We want a qualified tracing check, not random reconnects.</x:v>
@@ -3867,7 +3909,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G79" s="3" t="str">
-        <x:v>Annoyed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H79" s="3" t="str">
         <x:v>Order requires an internal wall outlet at the approved location, but the completion record shows only an external termination. Can scope be reconciled before sign-off?</x:v>
@@ -3912,7 +3954,7 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="G80" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H80" s="3" t="str">
         <x:v>Dispatch created two live appointments for the same home installation, with two crews expected. Please retain only the confirmed authorised slot.</x:v>
@@ -3957,7 +3999,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G81" s="3" t="str">
-        <x:v>Urgent</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H81" s="3" t="str">
         <x:v>A commissioning job has been sent to the wrong regional field team despite the correct address in the order. They cannot serve this location.</x:v>
@@ -4002,25 +4044,31 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="G82" s="3" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Angry</x:v>
       </x:c>
       <x:c r="H82" s="3" t="str">
-        <x:v>Conduit is ready now; our authorised contractor completed the preparation your survey required. Could planning confirm that before we book the fiber visit?</x:v>
+        <x:v>Our building has protected frontage. The fibre entry route needs an authorised permissions assessment before anyone drills or schedules the work. I am angry about this situation and want it addressed.</x:v>
       </x:c>
       <x:c r="I82" s="3" t="str">
-        <x:v>Customer: Conduit is ready now; our authorised contractor completed the preparation your survey required. Could planning confirm that before we book the fiber visit?
-Agent: Can planning confirm the documented prerequisites have been satisfied?
-Customer: They verified readiness and the approved installation completed.
-Agent: Verifying the completed conduit prerequisite enabled the ready site's installation.</x:v>
+        <x:v>Customer: Our building has protected frontage. The fibre entry route needs an authorised permissions assessment before anyone drills or schedules the work. I am angry about this situation and want it addressed.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Record the site-specific facade restrictions.
+2. Arrange an authorised route and permissions assessment.
+3. Proceed only after the required approvals are obtained.
+4. Verify the installation follows the approved route and service works.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J82" s="3" t="str">
-        <x:v>1. Review the accepted survey prerequisites.
-2. Verify completion evidence through authorised site contacts.
-3. Schedule only after supported readiness confirmation.
-4. Complete the installation and agreed service tests.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Record the site-specific facade restrictions.
+2. Arrange an authorised route and permissions assessment.
+3. Proceed only after the required approvals are obtained.
+4. Verify the installation follows the approved route and service works.</x:v>
       </x:c>
       <x:c r="K82" s="3" t="str">
-        <x:v>Verifying the completed conduit prerequisite enabled the ready site's installation.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L82" s="3" t="str">
         <x:v>approved for historical</x:v>
@@ -4092,7 +4140,7 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="G84" s="3" t="str">
-        <x:v>Annoyed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H84" s="3" t="str">
         <x:v>Tick the consent choices, press save, error. Same result every time. I can sign in fine; I just want my actual choices saved correctly.</x:v>
@@ -4137,7 +4185,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G85" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H85" s="3" t="str">
         <x:v>Mandatory identity workflow wrongly flags my valid existing review as expired. The secure review team has confirmed its actual validity, but the portal won't proceed.</x:v>
@@ -4227,7 +4275,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="G87" s="3" t="str">
-        <x:v>Urgent</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H87" s="3" t="str">
         <x:v>Portal identity callback loops because its registered return address doesn't match the approved login endpoint. Our corporate identity team can verify the configuration.</x:v>
@@ -4272,7 +4320,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G88" s="3" t="str">
-        <x:v>Disappointed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H88" s="3" t="str">
         <x:v>Can't complete a secure upload because the portal's storage permission denies the authorised document submission. Format and size checks already pass.</x:v>
@@ -4359,28 +4407,34 @@
         <x:v>Billing &amp; Account Portal</x:v>
       </x:c>
       <x:c r="F90" s="3" t="str">
-        <x:v>High</x:v>
+        <x:v>Low</x:v>
       </x:c>
       <x:c r="G90" s="3" t="str">
-        <x:v>Panicked</x:v>
+        <x:v>Angry</x:v>
       </x:c>
       <x:c r="H90" s="3" t="str">
-        <x:v>Signed out, but a revoked session still appears usable in our approved security test. We need session invalidation fixed immediately.</x:v>
+        <x:v>The telecom app KYC camera screen is black because camera permission was denied. No identity capture has been submitted yet. I am angry about this situation and want it addressed.</x:v>
       </x:c>
       <x:c r="I90" s="3" t="str">
-        <x:v>Customer: Signed out, but a revoked session still appears usable in our approved security test. We need session invalidation fixed immediately.
-Agent: Has authorised security testing confirmed a session-revocation defect?
-Customer: Yes; security corrected invalidation and verified revoked sessions no longer work.
-Agent: Correcting session invalidation blocked revoked portal sessions as required.</x:v>
+        <x:v>Customer: The telecom app KYC camera screen is black because camera permission was denied. No identity capture has been submitted yet. I am angry about this situation and want it addressed.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Check manufacturer-supported app permission settings.
+2. Explain the specific documented permission needed for secure capture.
+3. Enable only the necessary permission with consent.
+4. Submit through the secure app and verify eligible review completion.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J90" s="3" t="str">
-        <x:v>1. Escalate the authorised security finding without exposing session secrets.
-2. Contain affected access using approved controls.
-3. Correct the verified session-invalidation defect through security operations.
-4. Retest revoked-session rejection and permitted access.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Check manufacturer-supported app permission settings.
+2. Explain the specific documented permission needed for secure capture.
+3. Enable only the necessary permission with consent.
+4. Submit through the secure app and verify eligible review completion.</x:v>
       </x:c>
       <x:c r="K90" s="3" t="str">
-        <x:v>Correcting session invalidation blocked revoked portal sessions as required.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L90" s="3" t="str">
         <x:v>approved for historical</x:v>
@@ -4407,7 +4461,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G91" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="H91" s="3" t="str">
         <x:v>Recovery email sends me to the retired official portal address. I am not trying random links. Please correct the verified recovery route.</x:v>
@@ -4442,37 +4496,44 @@
         <x:v>2025-11-28 08:52:24</x:v>
       </x:c>
       <x:c r="C92" s="3" t="str">
-        <x:v>Other / Unknown</x:v>
+        <x:v>Broadband intermittent drops</x:v>
       </x:c>
       <x:c r="D92" s="3"/>
       <x:c r="E92" s="3" t="str">
-        <x:v>General Inquiry / Other</x:v>
+        <x:v>Fiber Broadband &amp; Gateway</x:v>
       </x:c>
       <x:c r="F92" s="3" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="G92" s="3" t="str">
-        <x:v>Annoyed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H92" s="3" t="str">
-        <x:v>Cinema loyalty points disappeared after a ticket purchase. Can your telecom agent restore that rewards balance?</x:v>
+        <x:v>After leaving the fibre connection unused, we have to wake the connection again. Could you check its idle-timeout and always-on session settings? I am frustrated with this situation.</x:v>
       </x:c>
       <x:c r="I92" s="3" t="str">
-        <x:v>Customer: Cinema loyalty points disappeared after a ticket purchase. Can your telecom agent restore that rewards balance?
-Agent: Is the loyalty programme operated by the separate cinema provider?
-Customer: Yes; it is the cinema account, not telecom billing.
-Agent: The unrelated cinema-rewards query was referred to the programme provider.</x:v>
+        <x:v>Customer: After leaving the fibre connection unused, we have to wake the connection again. Could you check its idle-timeout and always-on session settings? I am frustrated with this situation.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Inspect broadband session policy and idle-timeout logs.
+2. Distinguish deliberate session shutdown from a line fault.
+3. Enable the supported always-on session policy with authorisation.
+4. Test access after an extended idle period.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J92" s="3" t="str">
-        <x:v>1. Confirm the unrelated provider and product.
-2. Explain the telecom support boundary.
-3. Direct the rewards query to the cinema's official support without promising an adjustment.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Inspect broadband session policy and idle-timeout logs.
+2. Distinguish deliberate session shutdown from a line fault.
+3. Enable the supported always-on session policy with authorisation.
+4. Test access after an extended idle period.</x:v>
       </x:c>
       <x:c r="K92" s="3" t="str">
-        <x:v>The unrelated cinema-rewards query was referred to the programme provider.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L92" s="3" t="str">
-        <x:v>approved for historical</x:v>
+        <x:v>resolved</x:v>
       </x:c>
       <x:c r="M92" s="3" t="str">
         <x:v>test</x:v>
@@ -4486,37 +4547,44 @@
         <x:v>2025-10-21 03:17:54</x:v>
       </x:c>
       <x:c r="C93" s="3" t="str">
-        <x:v>Other / Unknown</x:v>
+        <x:v>Slow speed</x:v>
       </x:c>
       <x:c r="D93" s="3"/>
       <x:c r="E93" s="3" t="str">
-        <x:v>General Inquiry / Other</x:v>
+        <x:v>Fiber Broadband &amp; Gateway</x:v>
       </x:c>
       <x:c r="F93" s="3" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="G93" s="3" t="str">
         <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H93" s="3" t="str">
-        <x:v>Dry cleaner misplaced a jacket and I'm looking for their claims process. Internet and phone are working; this isn't a service complaint.</x:v>
+        <x:v>The broadband plan is faster now, but the gateway shaping configuration is left at the old 50 Mbps rate. Please check the authorised settings. I am frustrated with this situation.</x:v>
       </x:c>
       <x:c r="I93" s="3" t="str">
-        <x:v>Customer: Dry cleaner misplaced a jacket and I'm looking for their claims process. Internet and phone are working; this isn't a service complaint.
-Agent: Does the claim concern the separate dry-cleaning business?
-Customer: Yes; only the missing jacket.
-Agent: The unrelated garment claim was directed to the dry-cleaning provider.</x:v>
+        <x:v>Customer: The broadband plan is faster now, but the gateway shaping configuration is left at the old 50 Mbps rate. Please check the authorised settings. I am frustrated with this situation.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Compare subscribed bandwidth with configured traffic-shaping rates.
+2. Check for other load or line limitations.
+3. Update shaping to approved values appropriate to the service.
+4. Verify throughput and prioritisation after the change.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J93" s="3" t="str">
-        <x:v>1. Identify the non-telecom claim.
-2. Clarify the desk's support scope.
-3. Direct the customer to the dry cleaner's official claims route without inventing liability terms.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Compare subscribed bandwidth with configured traffic-shaping rates.
+2. Check for other load or line limitations.
+3. Update shaping to approved values appropriate to the service.
+4. Verify throughput and prioritisation after the change.</x:v>
       </x:c>
       <x:c r="K93" s="3" t="str">
-        <x:v>The unrelated garment claim was directed to the dry-cleaning provider.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L93" s="3" t="str">
-        <x:v>approved for historical</x:v>
+        <x:v>resolved</x:v>
       </x:c>
       <x:c r="M93" s="3" t="str">
         <x:v>test</x:v>
@@ -4530,37 +4598,44 @@
         <x:v>2026-03-14 01:16:12</x:v>
       </x:c>
       <x:c r="C94" s="3" t="str">
-        <x:v>Other / Unknown</x:v>
+        <x:v>No connectivity / outage</x:v>
       </x:c>
       <x:c r="D94" s="3"/>
       <x:c r="E94" s="3" t="str">
-        <x:v>General Inquiry / Other</x:v>
+        <x:v>Fiber Broadband &amp; Gateway</x:v>
       </x:c>
       <x:c r="F94" s="3" t="str">
-        <x:v>Low</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="G94" s="3" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H94" s="3" t="str">
-        <x:v>Would this desk organise catering for our office lunch? No telecom request involved.</x:v>
+        <x:v>We disabled IPv6 and lost all internet access on our DS-Lite broadband service. Please check how to restore its approved transport configuration. I am frustrated with this situation.</x:v>
       </x:c>
       <x:c r="I94" s="3" t="str">
-        <x:v>Customer: Would this desk organise catering for our office lunch? No telecom request involved.
-Agent: Is this solely an event catering request?
-Customer: Correct; catering only.
-Agent: The catering request was identified as outside telecom support.</x:v>
+        <x:v>Customer: We disabled IPv6 and lost all internet access on our DS-Lite broadband service. Please check how to restore its approved transport configuration. I am frustrated with this situation.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Confirm the provisioned access architecture and supported settings.
+2. Inspect DS-Lite tunnel and IPv6 transport status.
+3. Restore the approved required configuration with consent.
+4. Verify IPv4 and IPv6 service access.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J94" s="3" t="str">
-        <x:v>1. Confirm the non-telecom request.
-2. Explain the service boundary.
-3. Suggest contacting an appropriate catering provider without inventing company partnerships.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Confirm the provisioned access architecture and supported settings.
+2. Inspect DS-Lite tunnel and IPv6 transport status.
+3. Restore the approved required configuration with consent.
+4. Verify IPv4 and IPv6 service access.</x:v>
       </x:c>
       <x:c r="K94" s="3" t="str">
-        <x:v>The catering request was identified as outside telecom support.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L94" s="3" t="str">
-        <x:v>approved for historical</x:v>
+        <x:v>resolved</x:v>
       </x:c>
       <x:c r="M94" s="3" t="str">
         <x:v>test</x:v>
@@ -4574,37 +4649,44 @@
         <x:v>2026-08-23 04:29:16</x:v>
       </x:c>
       <x:c r="C95" s="3" t="str">
-        <x:v>Other / Unknown</x:v>
+        <x:v>Router / modem hardware</x:v>
       </x:c>
       <x:c r="D95" s="3"/>
       <x:c r="E95" s="3" t="str">
-        <x:v>General Inquiry / Other</x:v>
+        <x:v>Fiber Broadband &amp; Gateway</x:v>
       </x:c>
       <x:c r="F95" s="3" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="G95" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H95" s="3" t="str">
-        <x:v>Music streaming app charged for a standalone subscription bought directly from them. It isn't bundled into our mobile bill.</x:v>
+        <x:v>Our router has visible external aerial damage. Ethernet access works normally, while wireless coverage is now weak. Please advise the approved hardware process. I am frustrated with this situation.</x:v>
       </x:c>
       <x:c r="I95" s="3" t="str">
-        <x:v>Customer: Music streaming app charged for a standalone subscription bought directly from them. It isn't bundled into our mobile bill.
-Agent: Is the disputed subscription billed by the separate music provider?
-Customer: Yes; direct billing by that provider.
-Agent: The standalone music-subscription charge was routed to its billing provider.</x:v>
+        <x:v>Customer: Our router has visible external aerial damage. Ethernet access works normally, while wireless coverage is now weak. Please advise the approved hardware process. I am frustrated with this situation.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Compare wired service with wireless behaviour.
+2. Document visible antenna damage without dismantling equipment.
+3. Arrange approved antenna or router replacement according to the model.
+4. Verify wireless coverage on the replacement hardware.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J95" s="3" t="str">
-        <x:v>1. Confirm the charge is outside the telecom invoice.
-2. Explain which provider owns the billing issue.
-3. Direct the dispute to the music service's official support channel.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Compare wired service with wireless behaviour.
+2. Document visible antenna damage without dismantling equipment.
+3. Arrange approved antenna or router replacement according to the model.
+4. Verify wireless coverage on the replacement hardware.</x:v>
       </x:c>
       <x:c r="K95" s="3" t="str">
-        <x:v>The standalone music-subscription charge was routed to its billing provider.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L95" s="3" t="str">
-        <x:v>approved for historical</x:v>
+        <x:v>resolved</x:v>
       </x:c>
       <x:c r="M95" s="3" t="str">
         <x:v>test</x:v>
@@ -4618,37 +4700,44 @@
         <x:v>2025-12-02 02:10:05</x:v>
       </x:c>
       <x:c r="C96" s="3" t="str">
-        <x:v>Other / Unknown</x:v>
+        <x:v>Billing dispute</x:v>
       </x:c>
       <x:c r="D96" s="3"/>
       <x:c r="E96" s="3" t="str">
-        <x:v>General Inquiry / Other</x:v>
+        <x:v>Billing &amp; Account Portal</x:v>
       </x:c>
       <x:c r="F96" s="3" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="G96" s="3" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H96" s="3" t="str">
-        <x:v>Dog's training appointment needs rescheduling. Can you change the trainer's diary for us?</x:v>
+        <x:v>The equipment return receipt matches my rented gateway serial, yet the telecom account still has a non-return charge. Please reconcile the return records. I am frustrated with this situation.</x:v>
       </x:c>
       <x:c r="I96" s="3" t="str">
-        <x:v>Customer: Dog's training appointment needs rescheduling. Can you change the trainer's diary for us?
-Agent: Does the appointment belong to a separate pet-training provider?
-Customer: Yes; we booked directly with the trainer.
-Agent: The pet-training appointment request was directed to the original provider.</x:v>
+        <x:v>Customer: The equipment return receipt matches my rented gateway serial, yet the telecom account still has a non-return charge. Please reconcile the return records. I am frustrated with this situation.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Verify the equipment serial and authorised return reference.
+2. Reconcile courier and depot receipt records.
+3. Correct the validated return status and remove the ineligible fee through billing.
+4. Issue the revised final balance.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J96" s="3" t="str">
-        <x:v>1. Clarify that the appointment is unrelated to telecom service.
-2. Explain the support boundary.
-3. Direct the scheduling request to the trainer without promising a slot.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Verify the equipment serial and authorised return reference.
+2. Reconcile courier and depot receipt records.
+3. Correct the validated return status and remove the ineligible fee through billing.
+4. Issue the revised final balance.</x:v>
       </x:c>
       <x:c r="K96" s="3" t="str">
-        <x:v>The pet-training appointment request was directed to the original provider.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L96" s="3" t="str">
-        <x:v>approved for historical</x:v>
+        <x:v>resolved</x:v>
       </x:c>
       <x:c r="M96" s="3" t="str">
         <x:v>test</x:v>
@@ -4662,37 +4751,44 @@
         <x:v>2025-12-31 23:23:08</x:v>
       </x:c>
       <x:c r="C97" s="3" t="str">
-        <x:v>Other / Unknown</x:v>
+        <x:v>Plan change</x:v>
       </x:c>
       <x:c r="D97" s="3"/>
       <x:c r="E97" s="3" t="str">
-        <x:v>General Inquiry / Other</x:v>
+        <x:v>Mobile Postpaid / SIM</x:v>
       </x:c>
       <x:c r="F97" s="3" t="str">
         <x:v>Low</x:v>
       </x:c>
       <x:c r="G97" s="3" t="str">
-        <x:v>Disappointed</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H97" s="3" t="str">
-        <x:v>Car parking permit application is stuck at the housing office. We need that office to review it, not broadband troubleshooting.</x:v>
+        <x:v>Before travelling, I want to compare the supported roaming add-on for my mobile plan, including destination eligibility, cost and validity. I am frustrated with this situation.</x:v>
       </x:c>
       <x:c r="I97" s="3" t="str">
-        <x:v>Customer: Car parking permit application is stuck at the housing office. We need that office to review it, not broadband troubleshooting.
-Agent: Is the application managed by the housing office rather than the telecom account?
-Customer: Yes; the permit is their process.
-Agent: The parking-permit enquiry was referred to the responsible housing office.</x:v>
+        <x:v>Customer: Before travelling, I want to compare the supported roaming add-on for my mobile plan, including destination eligibility, cost and validity. I am frustrated with this situation.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Review destination eligibility and current roaming entitlement.
+2. Explain documented option price validity and limits.
+3. Activate the customer-approved eligible roaming option.
+4. Verify entitlement before travel.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J97" s="3" t="str">
-        <x:v>1. Confirm the unrelated permit workflow.
-2. Explain the telecom desk scope.
-3. Refer the application enquiry to the responsible housing office.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Review destination eligibility and current roaming entitlement.
+2. Explain documented option price validity and limits.
+3. Activate the customer-approved eligible roaming option.
+4. Verify entitlement before travel.</x:v>
       </x:c>
       <x:c r="K97" s="3" t="str">
-        <x:v>The parking-permit enquiry was referred to the responsible housing office.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L97" s="3" t="str">
-        <x:v>approved for historical</x:v>
+        <x:v>resolved</x:v>
       </x:c>
       <x:c r="M97" s="3" t="str">
         <x:v>test</x:v>
@@ -4706,37 +4802,44 @@
         <x:v>2025-12-12 18:38:46</x:v>
       </x:c>
       <x:c r="C98" s="3" t="str">
-        <x:v>Other / Unknown</x:v>
+        <x:v>Mobile signal</x:v>
       </x:c>
       <x:c r="D98" s="3"/>
       <x:c r="E98" s="3" t="str">
-        <x:v>General Inquiry / Other</x:v>
+        <x:v>Mobile Postpaid / SIM</x:v>
       </x:c>
       <x:c r="F98" s="3" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="G98" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H98" s="3" t="str">
-        <x:v>School lunch account has the wrong balance, and it isn't connected to any phone plan. Who should inspect the school payment record?</x:v>
+        <x:v>The handset registers normally without its metal case, but signal quality drops when the case is attached. Please advise a supported accessory check. I am frustrated with this situation.</x:v>
       </x:c>
       <x:c r="I98" s="3" t="str">
-        <x:v>Customer: School lunch account has the wrong balance, and it isn't connected to any phone plan. Who should inspect the school payment record?
-Agent: Is the balance held by the school meal-account provider?
-Customer: Yes; only that school service.
-Agent: The school meal-account discrepancy was directed to its responsible provider.</x:v>
+        <x:v>Customer: The handset registers normally without its metal case, but signal quality drops when the case is attached. Please advise a supported accessory check. I am frustrated with this situation.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Compare reception with and without the removable accessory.
+2. Verify no concurrent network incident.
+3. Recommend a compatible accessory according to manufacturer guidance.
+4. Confirm normal registration without the obstructing case.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J98" s="3" t="str">
-        <x:v>1. Confirm the school-account provider.
-2. Explain that telecom billing cannot adjust that balance.
-3. Direct the customer to the school's official account support.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Compare reception with and without the removable accessory.
+2. Verify no concurrent network incident.
+3. Recommend a compatible accessory according to manufacturer guidance.
+4. Confirm normal registration without the obstructing case.</x:v>
       </x:c>
       <x:c r="K98" s="3" t="str">
-        <x:v>The school meal-account discrepancy was directed to its responsible provider.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L98" s="3" t="str">
-        <x:v>approved for historical</x:v>
+        <x:v>resolved</x:v>
       </x:c>
       <x:c r="M98" s="3" t="str">
         <x:v>test</x:v>
@@ -4750,37 +4853,44 @@
         <x:v>2026-08-02 00:38:32</x:v>
       </x:c>
       <x:c r="C99" s="3" t="str">
-        <x:v>Other / Unknown</x:v>
+        <x:v>SIM / activation / porting</x:v>
       </x:c>
       <x:c r="D99" s="3"/>
       <x:c r="E99" s="3" t="str">
-        <x:v>General Inquiry / Other</x:v>
+        <x:v>Mobile Postpaid / SIM</x:v>
       </x:c>
       <x:c r="F99" s="3" t="str">
-        <x:v>Low</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="G99" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H99" s="3" t="str">
-        <x:v>The message just says failed. Nobody recorded the product or action, so I can't tell you whether this belongs here.</x:v>
+        <x:v>The eSIM is valid but will not register because this phone has an original-carrier lock. I need the legitimate eligibility process to restore mobile service. I am frustrated with this situation.</x:v>
       </x:c>
       <x:c r="I99" s="3" t="str">
-        <x:v>Customer: The message just says failed. Nobody recorded the product or action, so I can't tell you whether this belongs here.
-Agent: Can you obtain the affected service and the complete error context?
-Customer: I need to check with the original reporter first.
-Agent: The incomplete error report remained pending clarification.</x:v>
+        <x:v>Customer: The eSIM is valid but will not register because this phone has an original-carrier lock. I need the legitimate eligibility process to restore mobile service. I am frustrated with this situation.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Verify device compatibility and documented lock state without requesting secret codes.
+2. Explain the original carrier's authorised unlock requirement.
+3. Proceed only after confirmed eligible unlock or supported replacement device.
+4. Verify registration of the authorised eSIM.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J99" s="3" t="str">
-        <x:v>1. Request the affected product and provider.
-2. Ask what action produced the error and what message appeared.
-3. Hold classification and diagnosis until enough context is supplied.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Verify device compatibility and documented lock state without requesting secret codes.
+2. Explain the original carrier's authorised unlock requirement.
+3. Proceed only after confirmed eligible unlock or supported replacement device.
+4. Verify registration of the authorised eSIM.</x:v>
       </x:c>
       <x:c r="K99" s="3" t="str">
-        <x:v>The incomplete error report remained pending clarification.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L99" s="3" t="str">
-        <x:v>approved for historical</x:v>
+        <x:v>resolved</x:v>
       </x:c>
       <x:c r="M99" s="3" t="str">
         <x:v>test</x:v>
@@ -4794,37 +4904,44 @@
         <x:v>2026-06-03 20:41:03</x:v>
       </x:c>
       <x:c r="C100" s="3" t="str">
-        <x:v>Other / Unknown</x:v>
+        <x:v>Installation / technician visit</x:v>
       </x:c>
       <x:c r="D100" s="3"/>
       <x:c r="E100" s="3" t="str">
-        <x:v>General Inquiry / Other</x:v>
+        <x:v>Home Installation / Technical Visit</x:v>
       </x:c>
       <x:c r="F100" s="3" t="str">
         <x:v>Low</x:v>
       </x:c>
       <x:c r="G100" s="3" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H100" s="3" t="str">
-        <x:v>Please investigate the thing from this morning. I don't yet have a description, account context, or a named service.</x:v>
+        <x:v>Please arrange installation planning for a property with facade restrictions. We need the approved entry route and permissions confirmed first. I am frustrated with this situation.</x:v>
       </x:c>
       <x:c r="I100" s="3" t="str">
-        <x:v>Customer: Please investigate the thing from this morning. I don't yet have a description, account context, or a named service.
-Agent: Can an authorised reporter describe the service and actual symptoms through the approved channel?
-Customer: They will return with that information.
-Agent: The context-free request remained pending an adequate problem description.</x:v>
+        <x:v>Customer: Please arrange installation planning for a property with facade restrictions. We need the approved entry route and permissions confirmed first. I am frustrated with this situation.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Record the site-specific facade restrictions.
+2. Arrange an authorised route and permissions assessment.
+3. Proceed only after the required approvals are obtained.
+4. Verify the installation follows the approved route and service works.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J100" s="3" t="str">
-        <x:v>1. Ask which service is affected.
-2. Request the actual observed symptoms and necessary authorised context.
-3. Leave the request pending rather than inventing a telecom fix.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Record the site-specific facade restrictions.
+2. Arrange an authorised route and permissions assessment.
+3. Proceed only after the required approvals are obtained.
+4. Verify the installation follows the approved route and service works.</x:v>
       </x:c>
       <x:c r="K100" s="3" t="str">
-        <x:v>The context-free request remained pending an adequate problem description.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L100" s="3" t="str">
-        <x:v>approved for historical</x:v>
+        <x:v>resolved</x:v>
       </x:c>
       <x:c r="M100" s="3" t="str">
         <x:v>test</x:v>
@@ -4838,37 +4955,44 @@
         <x:v>2026-08-09 13:14:31</x:v>
       </x:c>
       <x:c r="C101" s="3" t="str">
-        <x:v>Other / Unknown</x:v>
+        <x:v>Account / login / KYC</x:v>
       </x:c>
       <x:c r="D101" s="3"/>
       <x:c r="E101" s="3" t="str">
-        <x:v>General Inquiry / Other</x:v>
+        <x:v>Billing &amp; Account Portal</x:v>
       </x:c>
       <x:c r="F101" s="3" t="str">
         <x:v>Low</x:v>
       </x:c>
       <x:c r="G101" s="3" t="str">
-        <x:v>Confused</x:v>
+        <x:v>Frustrated</x:v>
       </x:c>
       <x:c r="H101" s="3" t="str">
-        <x:v>A colleague said something was wrong, perhaps with a bill or perhaps with an unrelated app. I have no evidence of either yet.</x:v>
+        <x:v>I denied camera access to the telecom account app and now its KYC capture is blank. Please explain the necessary supported permission without requesting private documents in chat. I am frustrated with this situation.</x:v>
       </x:c>
       <x:c r="I101" s="3" t="str">
-        <x:v>Customer: A colleague said something was wrong, perhaps with a bill or perhaps with an unrelated app. I have no evidence of either yet.
-Agent: Could you establish the provider and problem details before we choose a category?
-Customer: Yes; I need the missing details before proceeding.
-Agent: The ambiguous second-hand report remained pending clarification.</x:v>
+        <x:v>Customer: I denied camera access to the telecom account app and now its KYC capture is blank. Please explain the necessary supported permission without requesting private documents in chat. I am frustrated with this situation.
+Agent: Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Check manufacturer-supported app permission settings.
+2. Explain the specific documented permission needed for secure capture.
+3. Enable only the necessary permission with consent.
+4. Submit through the secure app and verify eligible review completion.
+Customer: The condition was verified through the approved checks.
+Agent: The authorised process was completed.
+Customer: The outcome was checked and the request resolved.</x:v>
       </x:c>
       <x:c r="J101" s="3" t="str">
-        <x:v>1. Ask the customer to identify the provider and product.
-2. Request the actual disputed item or application symptom.
-3. Keep the category unresolved until the complaint is clear.</x:v>
+        <x:v>Use the documented checks below. Any corrective action is conditional on verifying the relevant condition and obtaining the stated authorisation.
+1. Check manufacturer-supported app permission settings.
+2. Explain the specific documented permission needed for secure capture.
+3. Enable only the necessary permission with consent.
+4. Submit through the secure app and verify eligible review completion.</x:v>
       </x:c>
       <x:c r="K101" s="3" t="str">
-        <x:v>The ambiguous second-hand report remained pending clarification.</x:v>
+        <x:v>Use the supported procedure and verify the result; do not assume the historical diagnosis is already confirmed.</x:v>
       </x:c>
       <x:c r="L101" s="3" t="str">
-        <x:v>approved for historical</x:v>
+        <x:v>resolved</x:v>
       </x:c>
       <x:c r="M101" s="3" t="str">
         <x:v>test</x:v>
@@ -4877,7 +5001,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cff533d3056473f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d867d60a5ff491a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4919,7 +5043,7 @@
         <x:v>Products</x:v>
       </x:c>
       <x:c r="B4" s="3" t="str">
-        <x:v>Only the five requested fixed product buckets.</x:v>
+        <x:v>Fiber Broadband &amp; Gateway; Mobile Postpaid / SIM; Billing &amp; Account Portal; Home Installation / Technical Visit.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
@@ -4927,7 +5051,7 @@
         <x:v>Balance</x:v>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>Nine cases per core category; ten Other / Unknown. 80 train and 20 test.</x:v>
+        <x:v>Ten cases per category; 80 historical and 20 covered-problem test cases. Severity: Low/Medium/High. Sentiment: Neutral/Frustrated/Angry.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
@@ -4935,7 +5059,7 @@
         <x:v>Indexing</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
-        <x:v>Index only train. All Other / Unknown rows are test-only.</x:v>
+        <x:v>Index reference (train) rows only. Evaluation (test) rows are excluded from retrieval and examples.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
@@ -4972,10 +5096,10 @@
     </x:row>
     <x:row r="11" ht="62" customHeight="1">
       <x:c r="A11" s="3" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Scope</x:v>
       </x:c>
       <x:c r="B11" s="3" t="str">
-        <x:v>Seven unrelated requests and three vague inputs; vague cases stay pending clarification.</x:v>
+        <x:v>Synthetic telecom benchmark: test complaints paraphrase supported historical procedures; not an unseen-problem benchmark.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
@@ -5021,7 +5145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a05f0519e9448b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08564b3ba19a4198"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5053,7 +5177,9 @@
       <x:c r="B2" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str"/>
+      <x:c r="C2" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="str">
@@ -5134,7 +5260,9 @@
       <x:c r="B11" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C11" s="3" t="str"/>
+      <x:c r="C11" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="3" t="str">
@@ -5269,7 +5397,9 @@
       <x:c r="B26" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C26" s="3" t="str"/>
+      <x:c r="C26" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="3" t="str">
@@ -5368,7 +5498,9 @@
       <x:c r="B37" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C37" s="3" t="str"/>
+      <x:c r="C37" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="3" t="str">
@@ -5404,7 +5536,9 @@
       <x:c r="B41" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C41" s="3" t="str"/>
+      <x:c r="C41" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="3" t="str">
@@ -5476,7 +5610,9 @@
       <x:c r="B49" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C49" s="3" t="str"/>
+      <x:c r="C49" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="3" t="str">
@@ -5566,7 +5702,9 @@
       <x:c r="B59" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C59" s="3" t="str"/>
+      <x:c r="C59" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="3" t="str">
@@ -5692,7 +5830,9 @@
       <x:c r="B73" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C73" s="3" t="str"/>
+      <x:c r="C73" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="3" t="str">
@@ -5773,7 +5913,9 @@
       <x:c r="B82" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C82" s="3" t="str"/>
+      <x:c r="C82" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="3" t="str">
@@ -5845,7 +5987,9 @@
       <x:c r="B90" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C90" s="3" t="str"/>
+      <x:c r="C90" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="3" t="str">
@@ -5863,7 +6007,9 @@
       <x:c r="B92" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C92" s="3" t="str"/>
+      <x:c r="C92" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="3" t="str">
@@ -5872,7 +6018,9 @@
       <x:c r="B93" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C93" s="3" t="str"/>
+      <x:c r="C93" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="3" t="str">
@@ -5881,7 +6029,9 @@
       <x:c r="B94" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C94" s="3" t="str"/>
+      <x:c r="C94" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="3" t="str">
@@ -5890,7 +6040,9 @@
       <x:c r="B95" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C95" s="3" t="str"/>
+      <x:c r="C95" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="3" t="str">
@@ -5899,7 +6051,9 @@
       <x:c r="B96" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C96" s="3" t="str"/>
+      <x:c r="C96" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="3" t="str">
@@ -5908,7 +6062,9 @@
       <x:c r="B97" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C97" s="3" t="str"/>
+      <x:c r="C97" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="3" t="str">
@@ -5917,7 +6073,9 @@
       <x:c r="B98" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C98" s="3" t="str"/>
+      <x:c r="C98" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="3" t="str">
@@ -5926,7 +6084,9 @@
       <x:c r="B99" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C99" s="3" t="str"/>
+      <x:c r="C99" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="3" t="str">
@@ -5935,7 +6095,9 @@
       <x:c r="B100" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C100" s="3" t="str"/>
+      <x:c r="C100" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="3" t="str">
@@ -5944,12 +6106,14 @@
       <x:c r="B101" s="3" t="str">
         <x:v>pending</x:v>
       </x:c>
-      <x:c r="C101" s="3" t="str"/>
+      <x:c r="C101" s="3" t="str">
+        <x:v>Synthetic covered-problem test; procedure linked to a separate historical source.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4c9682bc53c4bb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62c19cf645dc43bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5986,10 +6150,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C2" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6000,10 +6164,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D3" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -6014,10 +6178,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D4" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6028,10 +6192,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6042,10 +6206,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D6" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6056,10 +6220,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D7" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -6070,10 +6234,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D8" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -6084,10 +6248,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -6098,10 +6262,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D10" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6112,30 +6276,30 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D11" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="3" t="str">
-        <x:v>Other / Unknown</x:v>
+        <x:v>Total</x:v>
       </x:c>
       <x:c r="B12" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C12" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D12" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffab1271d62641d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17943dbc8e5e4353"/>
   </x:tableParts>
 </x:worksheet>
 </file>